--- a/artfynd/A 24126-2025 artfynd.xlsx
+++ b/artfynd/A 24126-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126544883</v>
       </c>
       <c r="B2" t="n">
-        <v>96487</v>
+        <v>96562</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>126531704</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>126531531</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>126531391</v>
       </c>
       <c r="B5" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126531754</v>
+        <v>126531473</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>442586</v>
+        <v>442562</v>
       </c>
       <c r="R6" t="n">
-        <v>6733372</v>
+        <v>6733341</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,9 +1171,19 @@
           <t>2025-07-09</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-07-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126531473</v>
+        <v>126531754</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1235,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>442562</v>
+        <v>442586</v>
       </c>
       <c r="R7" t="n">
-        <v>6733341</v>
+        <v>6733372</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1268,19 +1278,9 @@
           <t>2025-07-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>08:56</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-09</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>08:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,7 +1310,7 @@
         <v>126531405</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>126531717</v>
       </c>
       <c r="B9" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
